--- a/elite-data/manifest-templates/EL_template_AssayMicrobiomeTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AssayMicrobiomeTemplate.xlsx
@@ -142,7 +142,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="130">
   <si>
     <t>Filename</t>
   </si>
@@ -363,7 +363,7 @@
     <t>l</t>
   </si>
   <si>
-    <t>sac-seq</t>
+    <t>Qiagen Rneasy Extraction Kit</t>
   </si>
   <si>
     <t>M</t>
@@ -372,7 +372,7 @@
     <t>PCRfree</t>
   </si>
   <si>
-    <t>Smart-seq1</t>
+    <t>sac-seq</t>
   </si>
   <si>
     <t>mg</t>
@@ -381,7 +381,7 @@
     <t>polyAselection</t>
   </si>
   <si>
-    <t>Smart-seq2</t>
+    <t>Smart-seq1</t>
   </si>
   <si>
     <t>mg/dl</t>
@@ -390,7 +390,7 @@
     <t>proximity ligation</t>
   </si>
   <si>
-    <t>Smart-seq4</t>
+    <t>Smart-seq2</t>
   </si>
   <si>
     <t>mg/l</t>
@@ -399,7 +399,7 @@
     <t>rRNAdepletion</t>
   </si>
   <si>
-    <t>SMRTbell</t>
+    <t>Smart-seq4</t>
   </si>
   <si>
     <t>mg/ml</t>
@@ -408,7 +408,7 @@
     <t>snIsoSeq</t>
   </si>
   <si>
-    <t>TruSeq</t>
+    <t>SMRTbell</t>
   </si>
   <si>
     <t>miu/ml</t>
@@ -417,13 +417,16 @@
     <t>SPLITseq</t>
   </si>
   <si>
-    <t>Ultralow Methyl-Seq</t>
+    <t>TruSeq</t>
   </si>
   <si>
     <t>ml</t>
   </si>
   <si>
     <t>STARRSeq</t>
+  </si>
+  <si>
+    <t>Ultralow Methyl-Seq</t>
   </si>
   <si>
     <t>mM</t>
@@ -27917,6 +27920,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="N2:N1000">
       <formula1>Sheet2!$N$2:$N$59</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="P2:P1000">
+      <formula1>Sheet2!$P$2:$P$23</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="S2:S1000">
       <formula1>Sheet2!$S$2:$S$9</formula1>
     </dataValidation>
@@ -27928,9 +27934,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="V2:V1000">
       <formula1>Sheet2!$V$2:$V$8</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="P2:P1000">
-      <formula1>Sheet2!$P$2:$P$22</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId2"/>
@@ -28298,28 +28301,31 @@
         <v>93</v>
       </c>
       <c r="P22" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="N23" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="P23" s="7" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="23">
-      <c r="N23" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O23" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
     <row r="24">
       <c r="N24" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25">
       <c r="N25" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O25" s="7" t="s">
         <v>57</v>
@@ -28327,32 +28333,32 @@
     </row>
     <row r="26">
       <c r="N26" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
       <c r="N27" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28">
       <c r="N28" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29">
       <c r="N29" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30">
       <c r="N30" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31">
       <c r="N31" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32">
@@ -28372,122 +28378,122 @@
     </row>
     <row r="35">
       <c r="N35" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36">
       <c r="N36" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37">
       <c r="N37" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38">
       <c r="N38" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39">
       <c r="N39" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40">
       <c r="N40" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41">
       <c r="N41" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42">
       <c r="N42" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43">
       <c r="N43" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44">
       <c r="N44" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45">
       <c r="N45" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46">
       <c r="N46" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47">
       <c r="N47" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48">
       <c r="N48" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49">
       <c r="N49" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50">
       <c r="N50" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51">
       <c r="N51" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52">
       <c r="N52" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="53">
       <c r="N53" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54">
       <c r="N54" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="55">
       <c r="N55" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56">
       <c r="N56" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57">
       <c r="N57" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58">
       <c r="N58" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59">

--- a/elite-data/manifest-templates/EL_template_AssayMicrobiomeTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AssayMicrobiomeTemplate.xlsx
@@ -142,7 +142,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="129">
   <si>
     <t>Filename</t>
   </si>
@@ -303,7 +303,7 @@
     <t>stranded</t>
   </si>
   <si>
-    <t>singleEnd pairedEnd</t>
+    <t>Unknown</t>
   </si>
   <si>
     <t>gm</t>
@@ -313,9 +313,6 @@
   </si>
   <si>
     <t>NEBNext</t>
-  </si>
-  <si>
-    <t>Unknown</t>
   </si>
   <si>
     <t>HAU</t>
@@ -27927,6 +27924,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="P2:P1000">
       <formula1>Sheet2!$P$2:$P$23</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="V2:V1000">
+      <formula1>Sheet2!$V$2:$V$7</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="S2:S1000">
       <formula1>Sheet2!$S$2:$S$9</formula1>
     </dataValidation>
@@ -27935,9 +27935,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="R2:R1000">
       <formula1>Sheet2!$R$2:$R$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="V2:V1000">
-      <formula1>Sheet2!$V$2:$V$8</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId2"/>
@@ -28145,32 +28142,29 @@
         <v>56</v>
       </c>
       <c r="S8" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="N9" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="V8" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="N9" s="7" t="s">
+      <c r="O9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="O9" s="7" t="s">
+      <c r="P9" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="P9" s="7" t="s">
+      <c r="S9" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="S9" s="7" t="s">
+    </row>
+    <row r="10">
+      <c r="N10" s="7" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="N10" s="7" t="s">
+      <c r="O10" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>63</v>
       </c>
       <c r="P10" s="7" t="s">
         <v>30</v>
@@ -28178,10 +28172,10 @@
     </row>
     <row r="11">
       <c r="N11" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P11" s="7" t="s">
         <v>35</v>
@@ -28189,10 +28183,10 @@
     </row>
     <row r="12">
       <c r="N12" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P12" s="7" t="s">
         <v>39</v>
@@ -28200,169 +28194,169 @@
     </row>
     <row r="13">
       <c r="N13" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O13" s="7" t="s">
         <v>30</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14">
       <c r="N14" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O14" s="7" t="s">
         <v>35</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
       <c r="N15" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O15" s="7" t="s">
         <v>39</v>
       </c>
       <c r="P15" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="N16" s="7" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="N16" s="7" t="s">
+      <c r="O16" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="O16" s="7" t="s">
+      <c r="P16" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="P16" s="7" t="s">
+    </row>
+    <row r="17">
+      <c r="N17" s="7" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="N17" s="7" t="s">
+      <c r="O17" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="O17" s="7" t="s">
+      <c r="P17" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="P17" s="7" t="s">
+    </row>
+    <row r="18">
+      <c r="N18" s="7" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="N18" s="7" t="s">
+      <c r="O18" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="O18" s="7" t="s">
+      <c r="P18" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="P18" s="7" t="s">
+    </row>
+    <row r="19">
+      <c r="N19" s="7" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="N19" s="7" t="s">
+      <c r="O19" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="O19" s="7" t="s">
+      <c r="P19" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="P19" s="7" t="s">
+    </row>
+    <row r="20">
+      <c r="N20" s="7" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="N20" s="7" t="s">
+      <c r="O20" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="O20" s="7" t="s">
+      <c r="P20" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="P20" s="7" t="s">
+    </row>
+    <row r="21">
+      <c r="N21" s="7" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="N21" s="7" t="s">
+      <c r="O21" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="O21" s="7" t="s">
+      <c r="P21" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="P21" s="7" t="s">
+    </row>
+    <row r="22">
+      <c r="N22" s="7" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="N22" s="7" t="s">
+      <c r="O22" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="O22" s="7" t="s">
+      <c r="P22" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="P22" s="7" t="s">
+    </row>
+    <row r="23">
+      <c r="N23" s="7" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="N23" s="7" t="s">
+      <c r="O23" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="O23" s="7" t="s">
+      <c r="P23" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="N24" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="P23" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="N24" s="7" t="s">
+      <c r="O24" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="O24" s="7" t="s">
+    </row>
+    <row r="25">
+      <c r="N25" s="7" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="N25" s="7" t="s">
+      <c r="O25" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="N26" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="O25" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="N26" s="7" t="s">
+    </row>
+    <row r="27">
+      <c r="N27" s="7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="27">
-      <c r="N27" s="7" t="s">
+    <row r="28">
+      <c r="N28" s="7" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="28">
-      <c r="N28" s="7" t="s">
+    <row r="29">
+      <c r="N29" s="7" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="29">
-      <c r="N29" s="7" t="s">
+    <row r="30">
+      <c r="N30" s="7" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="30">
-      <c r="N30" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
     <row r="31">
       <c r="N31" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32">
@@ -28382,127 +28376,127 @@
     </row>
     <row r="35">
       <c r="N35" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="N36" s="7" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="36">
-      <c r="N36" s="7" t="s">
+    <row r="37">
+      <c r="N37" s="7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="37">
-      <c r="N37" s="7" t="s">
+    <row r="38">
+      <c r="N38" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="38">
-      <c r="N38" s="7" t="s">
+    <row r="39">
+      <c r="N39" s="7" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="39">
-      <c r="N39" s="7" t="s">
+    <row r="40">
+      <c r="N40" s="7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="40">
-      <c r="N40" s="7" t="s">
+    <row r="41">
+      <c r="N41" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="41">
-      <c r="N41" s="7" t="s">
+    <row r="42">
+      <c r="N42" s="7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="42">
-      <c r="N42" s="7" t="s">
+    <row r="43">
+      <c r="N43" s="7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="43">
-      <c r="N43" s="7" t="s">
+    <row r="44">
+      <c r="N44" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="44">
-      <c r="N44" s="7" t="s">
+    <row r="45">
+      <c r="N45" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="45">
-      <c r="N45" s="7" t="s">
+    <row r="46">
+      <c r="N46" s="7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="46">
-      <c r="N46" s="7" t="s">
+    <row r="47">
+      <c r="N47" s="7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="47">
-      <c r="N47" s="7" t="s">
+    <row r="48">
+      <c r="N48" s="7" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="48">
-      <c r="N48" s="7" t="s">
+    <row r="49">
+      <c r="N49" s="7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="49">
-      <c r="N49" s="7" t="s">
+    <row r="50">
+      <c r="N50" s="7" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="50">
-      <c r="N50" s="7" t="s">
+    <row r="51">
+      <c r="N51" s="7" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="51">
-      <c r="N51" s="7" t="s">
+    <row r="52">
+      <c r="N52" s="7" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="52">
-      <c r="N52" s="7" t="s">
+    <row r="53">
+      <c r="N53" s="7" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="53">
-      <c r="N53" s="7" t="s">
+    <row r="54">
+      <c r="N54" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="54">
-      <c r="N54" s="7" t="s">
+    <row r="55">
+      <c r="N55" s="7" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="55">
-      <c r="N55" s="7" t="s">
+    <row r="56">
+      <c r="N56" s="7" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="56">
-      <c r="N56" s="7" t="s">
+    <row r="57">
+      <c r="N57" s="7" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="57">
-      <c r="N57" s="7" t="s">
+    <row r="58">
+      <c r="N58" s="7" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="58">
-      <c r="N58" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
     <row r="59">
       <c r="N59" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/elite-data/manifest-templates/EL_template_AssayMicrobiomeTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AssayMicrobiomeTemplate.xlsx
@@ -234,7 +234,7 @@
     <t>forward</t>
   </si>
   <si>
-    <t>Not applicable</t>
+    <t>not applicable</t>
   </si>
   <si>
     <t>AI</t>
@@ -249,7 +249,7 @@
     <t>TRUE</t>
   </si>
   <si>
-    <t>Not collected</t>
+    <t>not collected</t>
   </si>
   <si>
     <t>AU/ml</t>
@@ -303,7 +303,7 @@
     <t>stranded</t>
   </si>
   <si>
-    <t>Unknown</t>
+    <t>unknown</t>
   </si>
   <si>
     <t>gm</t>
